--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>84.44081745868158</v>
+        <v>13.72163283703576</v>
       </c>
       <c r="D2" t="n">
-        <v>84.17121421438634</v>
+        <v>13.67782230983778</v>
       </c>
       <c r="E2" t="n">
-        <v>10.93594132783236</v>
+        <v>1.777090465772759</v>
       </c>
       <c r="F2" t="n">
-        <v>13.98318083236097</v>
+        <v>2.272266885258658</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.75957034118856</v>
+        <v>7.43593018044314</v>
       </c>
       <c r="D3" t="n">
-        <v>45.33471004102451</v>
+        <v>7.366890381666483</v>
       </c>
       <c r="E3" t="n">
-        <v>10.93594132783236</v>
+        <v>1.777090465772759</v>
       </c>
       <c r="F3" t="n">
-        <v>13.98318083236097</v>
+        <v>2.272266885258658</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>69.48491671794717</v>
+        <v>11.29129896666642</v>
       </c>
       <c r="D4" t="n">
-        <v>36.18768889241321</v>
+        <v>5.880499445017146</v>
       </c>
       <c r="E4" t="n">
-        <v>10.93594132783236</v>
+        <v>1.777090465772759</v>
       </c>
       <c r="F4" t="n">
-        <v>13.98318083236097</v>
+        <v>2.272266885258658</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>63.59533069274747</v>
+        <v>10.33424123757147</v>
       </c>
       <c r="D5" t="n">
-        <v>50.82926506306393</v>
+        <v>8.259755572747888</v>
       </c>
       <c r="E5" t="n">
-        <v>10.93594132783236</v>
+        <v>1.777090465772759</v>
       </c>
       <c r="F5" t="n">
-        <v>13.98318083236097</v>
+        <v>2.272266885258658</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>60.89096233789213</v>
+        <v>9.894781379907473</v>
       </c>
       <c r="D6" t="n">
-        <v>60.74818583298205</v>
+        <v>9.871580197859583</v>
       </c>
       <c r="E6" t="n">
-        <v>10.93594132783236</v>
+        <v>1.777090465772759</v>
       </c>
       <c r="F6" t="n">
-        <v>13.98318083236097</v>
+        <v>2.272266885258658</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>57.67654634932499</v>
+        <v>9.372438781765311</v>
       </c>
       <c r="D7" t="n">
-        <v>57.00756007922255</v>
+        <v>9.263728512873664</v>
       </c>
       <c r="E7" t="n">
-        <v>10.93594132783236</v>
+        <v>1.777090465772759</v>
       </c>
       <c r="F7" t="n">
-        <v>13.98318083236097</v>
+        <v>2.272266885258658</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>60.68432449262204</v>
+        <v>9.861202730051081</v>
       </c>
       <c r="D8" t="n">
-        <v>60.42236071880357</v>
+        <v>9.818633616805581</v>
       </c>
       <c r="E8" t="n">
-        <v>10.93594132783236</v>
+        <v>1.777090465772759</v>
       </c>
       <c r="F8" t="n">
-        <v>13.98318083236097</v>
+        <v>2.272266885258658</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
